--- a/data/merged/2026-09-28/MERGED_ES_Spot-Cleaner_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_ES_Spot-Cleaner_2026-09-28.xlsx
@@ -7721,50 +7721,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8090,7 +8046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18256,56 +18212,52 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0DDPL3PD2</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>Tamaño: 1.89 l (Paquete de 1)</t>
-        </is>
-      </c>
+          <t>B08KXVXC82</t>
+        </is>
+      </c>
+      <c r="D42" s="14"/>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Marca: Vacmaster | Forma del producto: Líquido | Aroma: Wildflower | Usos específicos del producto: Alfombrilla | Característica del material: Natural | Volumen del producto: 1892 Mililitros | Número de unidades: 1892.0 Millilitros | Número de productos: 1 | Contiene contenido líquido: Sí | Fabricante: Cleva</t>
+          <t>Marca: MEDION | Color: Gris | Peso del producto: 4,5 Kilogramos | Dimensiones del producto: 24f. x 31,7an. x 35al. centímetros | Nombre del modelo: MD 100122 | Capacidad: 1,08 litros | Número de unidades: 1.0 Conteo | Fabricante: MEDION | Número de productos: 1 | Destacado del artículo: Aspirador en húmedo para tejidos alfombras asientos, depósitos limpia y sucia, accesorio ventana, MD100122</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>MEDION</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Vacmaster/page/935EC746-F3AD-4C28-9B32-85256EBEE494?lp_asin=B0DDPL3PD2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/MEDION/page/674A7F5D-6984-42A5-8C9C-550514A9CEDC?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Clean &amp; Restore Carpet Cleaner Formula – CCS04</t>
+          <t>MEDION E10 UC Limpiador tapicería aspirador lavado - 750 W</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>Limpieza multisuperficie: Diseñado para ofrecer resultados de limpieza de alta calidad en una amplia gama de superficies, incluyendo alfombras, tapetes, tapicería del hogar e interiores de automóviles.
-Poder de limpieza profunda: Su potente fórmula penetra profundamente en las fibras, eliminando no solo la suciedad superficial, sino también las manchas difíciles.
-Elimina olores: Neutraliza una amplia gama de olores, dejando alfombras y tapicería frescas y limpias al instante.
-Protección contra derrames de mascotas: Diseñado especialmente para dueños de mascotas, este limpiador elimina eficazmente las manchas y los olores de las mascotas, creando un ambiente limpio y fresco.
-Compatibilidad: Apto para usar con la limpiadora de alfombras portátil Vacmaster (modelos SCA0801, SCB0501, SCC1201H, CA0701EU, DSC2401, VK1323PFR, VK1330PWR)</t>
+          <t>LIMPIEZA POTENTE: Hasta 750 W y aprox. 15 kPa de succión para eliminar manchas y suciedad incrustada de sofás, sillones, alfombras, moquetas y asientos de coche.
+DEPÓSITOS SEPARADOS: Depósito de agua limpia de aprox. 1080 ml y agua sucia de aprox. 730 ml para limpiar textiles durante más tiempo sin interrupciones frecuentes.
+PRÁCTICO A DIARIO: Asa de transporte, interruptor de encendido/apagado y cable de 5 m ofrecen un uso flexible en casa, taller o coche.
+COMPACTO Y MÓVIL: Tamaño de aprox. 32 × 24 × 35 cm y peso de aprox. 4,5 kg para transportar, guardar y usar fácilmente el limpiador textil.
+VERSÁTIL CON ACCESORIO: Accesorio para ventana incluido para cristales, espejos y mamparas de ducha, ideal para el mantenimiento del hogar y del coche.</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DDPL3PD2?psc=1</t>
+          <t>https://www.amazon.es/dp/B08KXVXC82?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0HJHD1BWJ</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -18319,13 +18271,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>9248</v>
+        <v>6892</v>
       </c>
       <c r="P42" s="15">
-        <v>-4048</v>
+        <v>37723</v>
       </c>
       <c r="Q42" s="16">
-        <v>-0.69</v>
+        <v>0.76</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -18334,61 +18286,55 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U42" s="16">
-        <v>0.12</v>
+        <v>-0.33</v>
       </c>
       <c r="V42" s="15">
-        <v>3858</v>
-      </c>
-      <c r="W42" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X42" s="15">
-        <v>1999</v>
-      </c>
+        <v>3777</v>
+      </c>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>19.99</v>
+        <v>69.95</v>
       </c>
       <c r="AA42" s="4"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>673</v>
+        <v>85</v>
       </c>
       <c r="AE42" s="15">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="AF42" s="21">
         <v>4.5</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.2073</v>
+        <v>0.3333</v>
       </c>
       <c r="AH42" s="20">
-        <v>5.58</v>
+        <v>9.06</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>765</v>
+        <v>159</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
@@ -18406,7 +18352,7 @@
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>medionshop-deutschland</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
@@ -18414,9 +18360,21 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="13"/>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>Essen 45307 DE</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
+        </is>
+      </c>
       <c r="AX42" s="13"/>
       <c r="AY42" s="13" t="inlineStr">
         <is>
@@ -18433,11 +18391,7 @@
       </c>
       <c r="BD42" s="13"/>
       <c r="BE42" s="13"/>
-      <c r="BF42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
       <c r="BI42" s="23" t="inlineStr">
@@ -18447,47 +18401,43 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2,03 kg</t>
+          <t>4,5 Kilogramos</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>25 x 16,8 x 7,6 cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 16.80 x 7.60 cm</t>
-        </is>
-      </c>
+          <t>24f. x 31,7an. x 35al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>2.03 kg</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>25 x 16.8 x 7.6 cm</t>
+          <t>37.6 x 37.1 x 26.9 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 16.80 x 7.60 cm</t>
+          <t>37.60 x 37.10 x 26.90 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18498,52 +18448,56 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
-        </is>
-      </c>
-      <c r="D43" s="14"/>
+          <t>B0GQGFSN4B</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Color: Orange</t>
+        </is>
+      </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>Marca: MEDION | Color: Gris | Peso del producto: 4,5 Kilogramos | Dimensiones del producto: 24f. x 31,7an. x 35al. centímetros | Nombre del modelo: MD 100122 | Capacidad: 1,08 litros | Número de unidades: 1.0 Conteo | Fabricante: MEDION | Número de productos: 1 | Destacado del artículo: Aspirador en húmedo para tejidos alfombras asientos, depósitos limpia y sucia, accesorio ventana, MD100122</t>
+          <t>Marca: X-cotec | Color: Orange | Nombre del modelo: C9S-P | Capacidad: 1550 ml | Fuente de alimentación: Cable eléctrico | Fabricante: Yantai Yunshengda Hardware Tools Co., Ltd | UPC: 729545258843 | Número de productos: 1</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>MEDION</t>
+          <t>X-cotec</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/MEDION/page/674A7F5D-6984-42A5-8C9C-550514A9CEDC?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.es/X-cotec/b/ref=bl_dp_s_web_83579058031?ie=UTF8&amp;node=83579058031&amp;field-lbr_brands_browse-bin=X-cotec</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>MEDION E10 UC Limpiador tapicería aspirador lavado - 750 W</t>
+          <t>Limpiador de Tapicerías 450W 13kPa, Aspiradora de Agua para Tapicería y Sofá, Máquina para Limpiar Sofás, Alfombras y Colchones, con 3 Cepillos y Doble Depósito Autolimpiable, Portátil 2,6kg</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>LIMPIEZA POTENTE: Hasta 750 W y aprox. 15 kPa de succión para eliminar manchas y suciedad incrustada de sofás, sillones, alfombras, moquetas y asientos de coche.
-DEPÓSITOS SEPARADOS: Depósito de agua limpia de aprox. 1080 ml y agua sucia de aprox. 730 ml para limpiar textiles durante más tiempo sin interrupciones frecuentes.
-PRÁCTICO A DIARIO: Asa de transporte, interruptor de encendido/apagado y cable de 5 m ofrecen un uso flexible en casa, taller o coche.
-COMPACTO Y MÓVIL: Tamaño de aprox. 32 × 24 × 35 cm y peso de aprox. 4,5 kg para transportar, guardar y usar fácilmente el limpiador textil.
-VERSÁTIL CON ACCESORIO: Accesorio para ventana incluido para cristales, espejos y mamparas de ducha, ideal para el mantenimiento del hogar y del coche.</t>
+          <t>✅【Motor de 450W y aspiración de 13kPa】 El potente motor de 450W combinado con la aspiración de 13kPa penetra profundamente en las fibras, eliminando fácilmente manchas difíciles, pelo de mascotas y malos olores. El sistema de limpieza de 3 pasos (pulverización, cepillado y aspiración) ofrece resultados visibles: tras la limpieza, los tejidos quedan como nuevos. Este limpiador de tapicerías y aspiradora de agua garantiza una limpieza profunda en sofás, alfombras y más.
+✅【3 cepillos profesionales para toda la casa】 Incluye un cepillo ancho para alfombras grandes, un cepillo estándar para manchas diarias en sofás y un cepillo multifunción 360° para rincones y asientos de coche. Con una sola máquina podrás limpiar sofás, alfombras, coche, cortinas y cualquier tejido del hogar sin dejar rincones sucios. Esta máquina para limpiar tapicerías es perfecta como limpiador de sofás y aspiradora para alfombras.
+✅【Depósitos de agua limpia y sucia separados + Autolimpieza con un botón】 El depósito de agua limpia de 1000 ml y el de agua sucia de 550 ml están completamente separados: el agua sucia nunca regresa al circuito, asegurando que siempre uses agua limpia. Tras la limpieza, coloca el cepillo en su lugar y presiona un botón para activar el sistema de autolimpieza que enjuaga automáticamente los tubos internos, previniendo bacterias y prolongando la vida útil. Esta aspiradora inyección extracción con doble depósito es la elección ideal.
+✅【Radio de acción de 5,5 m + Almacenamiento de manguera integrado】 Con un radio de 5,5 m (cable de 4 m + manguera de 1,5 m), podrás limpiar toda la sala de estar sin cambiar de enchufe. Después de usarlo, enrolla la manguera directamente en el cuerpo del aparato: adiós al desorden, siempre listo para usar. Esta aspiradora de agua para tapicerías portátil te brinda libertad de movimiento.
+✅【Solo 2,6 kg + Diseñado para hogares con mascotas】 Con solo 2,6 kg, es extremadamente ligero y fácil de transportar; incluso mujeres y personas mayores pueden usarlo con una sola mano. Diseñado especialmente para hogares con mascotas, elimina fácilmente el pelo, las huellas y los olores de mascotas en sofás, alfombras y asientos de coche. Incluye un detergente especial de 250 ml para que tu hogar recupere la frescura. Este limpiador de tapicerías para mascotas es el compañero perfecto.</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B08KXVXC82?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GQGFSN4B?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/418leHoiDxL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0GR8DLV1X</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -18557,13 +18511,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>6892</v>
+        <v>9080</v>
       </c>
       <c r="P43" s="15">
-        <v>37723</v>
+        <v>8966</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.76</v>
+        <v>0.19</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -18572,55 +18526,55 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="V43" s="15">
-        <v>3777</v>
+        <v>3491</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
       <c r="Y43" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="20">
-        <v>69.95</v>
+        <v>72.73</v>
       </c>
       <c r="AA43" s="4"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="19">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="AE43" s="15">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="21">
         <v>4.5</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="AH43" s="20">
-        <v>9.06</v>
+        <v>6.05</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -18630,15 +18584,13 @@
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43" s="20"/>
-      <c r="AQ43" s="19">
-        <v>9</v>
-      </c>
+      <c r="AQ43" s="19"/>
       <c r="AR43" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>medionshop-deutschland</t>
+          <t>INFINITE Electronic Commerce</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
@@ -18653,12 +18605,12 @@
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>Essen 45307 DE</t>
+          <t>Neuss 41460 DE</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3IGDW0WOTILEN</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
@@ -18675,7 +18627,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="13"/>
+      <c r="BD43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
@@ -18687,43 +18643,47 @@
       </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilogramos</t>
+          <t>3,88 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>3.88 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>24f. x 31,7an. x 35al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM43" s="23"/>
+          <t>35,5 x 32 x 19 cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="23" t="inlineStr">
+        <is>
+          <t>35.50 x 32.00 x 19.00 cm</t>
+        </is>
+      </c>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>3.88 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>3.88 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>37.6 x 37.1 x 26.9 cm</t>
+          <t>35.7 x 32.9 x 19.6 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>37.60 x 37.10 x 26.90 cm</t>
+          <t>35.70 x 32.90 x 19.60 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18734,277 +18694,31 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GQGFSN4B</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>Color: Orange</t>
-        </is>
-      </c>
+          <t>B0B3J3Q9RD</t>
+        </is>
+      </c>
+      <c r="D44" s="14"/>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Marca: X-cotec | Color: Orange | Nombre del modelo: C9S-P | Capacidad: 1550 ml | Fuente de alimentación: Cable eléctrico | Fabricante: Yantai Yunshengda Hardware Tools Co., Ltd | UPC: 729545258843 | Número de productos: 1</t>
+          <t>Marca: HAUSHOF | Color: Blanco/Gris | Peso del producto: 3,4 Kilogramos | Dimensiones del producto: 15f. x 28,5an. x 26,5al. centímetros | Estilo: Contemporáneo | Nombre del modelo: HAUSHOF Aspiradora de Agua Tapiceria | Capacidad: 1,1 litros | Fuente de alimentación: Cable | Fabricante: Hang Zhou Great Star Industrial Co.,LTD | UPC: 820909778370</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>X-cotec</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/X-cotec/b/ref=bl_dp_s_web_83579058031?ie=UTF8&amp;node=83579058031&amp;field-lbr_brands_browse-bin=X-cotec</t>
+          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Limpiador de Tapicerías 450W 13kPa, Aspiradora de Agua para Tapicería y Sofá, Máquina para Limpiar Sofás, Alfombras y Colchones, con 3 Cepillos y Doble Depósito Autolimpiable, Portátil 2,6kg</t>
+          <t>HAUSHOF StainZapper Aspiradora de Agua para Tapicerías, 400W</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>✅【Motor de 450W y aspiración de 13kPa】 El potente motor de 450W combinado con la aspiración de 13kPa penetra profundamente en las fibras, eliminando fácilmente manchas difíciles, pelo de mascotas y malos olores. El sistema de limpieza de 3 pasos (pulverización, cepillado y aspiración) ofrece resultados visibles: tras la limpieza, los tejidos quedan como nuevos. Este limpiador de tapicerías y aspiradora de agua garantiza una limpieza profunda en sofás, alfombras y más.
-✅【3 cepillos profesionales para toda la casa】 Incluye un cepillo ancho para alfombras grandes, un cepillo estándar para manchas diarias en sofás y un cepillo multifunción 360° para rincones y asientos de coche. Con una sola máquina podrás limpiar sofás, alfombras, coche, cortinas y cualquier tejido del hogar sin dejar rincones sucios. Esta máquina para limpiar tapicerías es perfecta como limpiador de sofás y aspiradora para alfombras.
-✅【Depósitos de agua limpia y sucia separados + Autolimpieza con un botón】 El depósito de agua limpia de 1000 ml y el de agua sucia de 550 ml están completamente separados: el agua sucia nunca regresa al circuito, asegurando que siempre uses agua limpia. Tras la limpieza, coloca el cepillo en su lugar y presiona un botón para activar el sistema de autolimpieza que enjuaga automáticamente los tubos internos, previniendo bacterias y prolongando la vida útil. Esta aspiradora inyección extracción con doble depósito es la elección ideal.
-✅【Radio de acción de 5,5 m + Almacenamiento de manguera integrado】 Con un radio de 5,5 m (cable de 4 m + manguera de 1,5 m), podrás limpiar toda la sala de estar sin cambiar de enchufe. Después de usarlo, enrolla la manguera directamente en el cuerpo del aparato: adiós al desorden, siempre listo para usar. Esta aspiradora de agua para tapicerías portátil te brinda libertad de movimiento.
-✅【Solo 2,6 kg + Diseñado para hogares con mascotas】 Con solo 2,6 kg, es extremadamente ligero y fácil de transportar; incluso mujeres y personas mayores pueden usarlo con una sola mano. Diseñado especialmente para hogares con mascotas, elimina fácilmente el pelo, las huellas y los olores de mascotas en sofás, alfombras y asientos de coche. Incluye un detergente especial de 250 ml para que tu hogar recupere la frescura. Este limpiador de tapicerías para mascotas es el compañero perfecto.</t>
-        </is>
-      </c>
-      <c r="J44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0GQGFSN4B?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/418leHoiDxL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="14" t="inlineStr">
-        <is>
-          <t>B0GR8DLV1X</t>
-        </is>
-      </c>
-      <c r="M44" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="N44" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O44" s="15">
-        <v>9080</v>
-      </c>
-      <c r="P44" s="15">
-        <v>8966</v>
-      </c>
-      <c r="Q44" s="16">
-        <v>0.19</v>
-      </c>
-      <c r="R44" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="S44" s="18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="T44" s="15">
-        <v>48</v>
-      </c>
-      <c r="U44" s="16">
-        <v>-0.32</v>
-      </c>
-      <c r="V44" s="15">
-        <v>3491</v>
-      </c>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z44" s="20">
-        <v>72.73</v>
-      </c>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="15"/>
-      <c r="AD44" s="19">
-        <v>71</v>
-      </c>
-      <c r="AE44" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="21">
-        <v>4.5</v>
-      </c>
-      <c r="AG44" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="20">
-        <v>6.05</v>
-      </c>
-      <c r="AI44" s="16">
-        <v>0.79</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AL44" s="19">
-        <v>211</v>
-      </c>
-      <c r="AM44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN44" s="13"/>
-      <c r="AO44" s="13"/>
-      <c r="AP44" s="20"/>
-      <c r="AQ44" s="19"/>
-      <c r="AR44" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS44" s="14" t="inlineStr">
-        <is>
-          <t>INFINITE Electronic Commerce</t>
-        </is>
-      </c>
-      <c r="AT44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>Neuss 41460 DE</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3IGDW0WOTILEN</t>
-        </is>
-      </c>
-      <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ44" s="13"/>
-      <c r="BA44" s="13"/>
-      <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE44" s="13"/>
-      <c r="BF44" s="13"/>
-      <c r="BG44" s="13"/>
-      <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
-      <c r="BJ44" s="23" t="inlineStr">
-        <is>
-          <t>3,88 kg</t>
-        </is>
-      </c>
-      <c r="BK44" s="23" t="inlineStr">
-        <is>
-          <t>3.88 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="23" t="inlineStr">
-        <is>
-          <t>35,5 x 32 x 19 cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="23" t="inlineStr">
-        <is>
-          <t>35.50 x 32.00 x 19.00 cm</t>
-        </is>
-      </c>
-      <c r="BN44" s="23" t="inlineStr">
-        <is>
-          <t>3.88 kg</t>
-        </is>
-      </c>
-      <c r="BO44" s="23" t="inlineStr">
-        <is>
-          <t>3.88 kg</t>
-        </is>
-      </c>
-      <c r="BP44" s="23" t="inlineStr">
-        <is>
-          <t>35.7 x 32.9 x 19.6 cm</t>
-        </is>
-      </c>
-      <c r="BQ44" s="23" t="inlineStr">
-        <is>
-          <t>35.70 x 32.90 x 19.60 cm</t>
-        </is>
-      </c>
-      <c r="BR44" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13">
-        <v>44</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>B0B3J3Q9RD</t>
-        </is>
-      </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Marca: HAUSHOF | Color: Blanco/Gris | Peso del producto: 3,4 Kilogramos | Dimensiones del producto: 15f. x 28,5an. x 26,5al. centímetros | Estilo: Contemporáneo | Nombre del modelo: HAUSHOF Aspiradora de Agua Tapiceria | Capacidad: 1,1 litros | Fuente de alimentación: Cable | Fabricante: Hang Zhou Great Star Industrial Co.,LTD | UPC: 820909778370</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>HAUSHOF</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>HAUSHOF StainZapper Aspiradora de Agua para Tapicerías, 400W</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>【Limpieza Potente】: Motor de 400W para una limpieza eficiente de alfombras, sofás, cojines y asientos de coche, reduciendo el tiempo en tareas domésticas.
 【Doble Tanque de Agua】: Depósitos extraíbles para agua limpia (1100 ml) y residuos (500 ml), permitiendo limpieza continua y almacenamiento separado de suciedad.
@@ -19013,19 +18727,255 @@
 【Bajo Ruido y Portátil】: Con nivel de ruido de 85 dB y peso de 3,4 kg, la limpiadora es silenciosa y fácil de transportar, con asa para acceder a todos los rincones.</t>
         </is>
       </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/dp/B0B3J3Q9RD?psc=1</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr">
+        <is>
+          <t>B0B3J3Q9RD</t>
+        </is>
+      </c>
+      <c r="M44" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
+        </is>
+      </c>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina</t>
+        </is>
+      </c>
+      <c r="O44" s="15">
+        <v>58252</v>
+      </c>
+      <c r="P44" s="15">
+        <v>-445</v>
+      </c>
+      <c r="Q44" s="16">
+        <v>-0.01</v>
+      </c>
+      <c r="R44" s="17" t="inlineStr">
+        <is>
+          <t>Aspiradoras para alfombras</t>
+        </is>
+      </c>
+      <c r="S44" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="T44" s="15">
+        <v>42</v>
+      </c>
+      <c r="U44" s="16">
+        <v>-0.14</v>
+      </c>
+      <c r="V44" s="15">
+        <v>3360</v>
+      </c>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
+      <c r="Y44" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="20">
+        <v>79.99</v>
+      </c>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="15"/>
+      <c r="AD44" s="19">
+        <v>4789</v>
+      </c>
+      <c r="AE44" s="15">
+        <v>34</v>
+      </c>
+      <c r="AF44" s="21">
+        <v>4.1</v>
+      </c>
+      <c r="AG44" s="22">
+        <v>0.8095</v>
+      </c>
+      <c r="AH44" s="20">
+        <v>8.37</v>
+      </c>
+      <c r="AI44" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="AJ44"/>
+      <c r="AK44" s="13" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AL44" s="19">
+        <v>1239</v>
+      </c>
+      <c r="AM44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN44" s="13"/>
+      <c r="AO44" s="13"/>
+      <c r="AP44" s="20"/>
+      <c r="AQ44" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR44" s="19">
+        <v>4</v>
+      </c>
+      <c r="AS44" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="AT44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU44" s="13"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="13"/>
+      <c r="AX44" s="13"/>
+      <c r="AY44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ44" s="13"/>
+      <c r="BA44" s="13"/>
+      <c r="BB44" s="13"/>
+      <c r="BC44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE44" s="13"/>
+      <c r="BF44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG44" s="13"/>
+      <c r="BH44" s="14"/>
+      <c r="BI44" s="23" t="inlineStr">
+        <is>
+          <t>Opción Amazon</t>
+        </is>
+      </c>
+      <c r="BJ44" s="23" t="inlineStr">
+        <is>
+          <t>3,4 Kilogramos</t>
+        </is>
+      </c>
+      <c r="BK44" s="23" t="inlineStr">
+        <is>
+          <t>3.40 kg</t>
+        </is>
+      </c>
+      <c r="BL44" s="23" t="inlineStr">
+        <is>
+          <t>15f. x 28,5an. x 26,5al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM44" s="23"/>
+      <c r="BN44" s="23" t="inlineStr">
+        <is>
+          <t>4.85 kg</t>
+        </is>
+      </c>
+      <c r="BO44" s="23" t="inlineStr">
+        <is>
+          <t>4.85 kg</t>
+        </is>
+      </c>
+      <c r="BP44" s="23" t="inlineStr">
+        <is>
+          <t>40.2 x 34.2 x 19.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ44" s="23" t="inlineStr">
+        <is>
+          <t>40.20 x 34.20 x 19.50 cm</t>
+        </is>
+      </c>
+      <c r="BR44" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>44</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>B0DX2J6DW2</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Set name: 1L solución de limpieza</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Marca: Akitas | Color: Azul | Peso del producto: 1,1 Kilogramos | Dimensiones del producto: 15f. x 27an. x 28al. centímetros | Estilo: Compacto | Nombre del modelo: X7 | Capacidad: 1 litros | Fuente de alimentación: Cable eléctrico | Número de unidades: 1000.0 Millilitros | Fabricante: Akitas</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Akitas</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>Akitas Limpiador para Moquetas y Tapicerías 1L Baja Espuma Fragancia Floral Para Alfombras Sofás Asientos de Coche Elimina Olores y Manchas de Mascotas</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza Profunda de Manchas y Olores：Fórmula profesional que elimina manchas difíciles de mascotas, restos de comida y olores incrustados en alfombras, sofás, moquetas, tapicerías y asientos de coche. Restaura la frescura original.
+Ultra Concentrado 1:25：1L rinde para 25L de solución. Solo diluye 1 parte del producto con 25 partes de agua. Máxima eficiencia y ahorro para limpiezas grandes o frecuentes.
+Baja Espuma y Seguro para Máquinas：Diseñado con fórmula de baja espuma para evitar exceso de burbujas. Compatible con todas las máquinas limpiadoras de alfombras. Seguro para el equipo y fácil de enjuagar.
+Suave con los Tejidos, Fuerte con la Suciedad：Apto para la mayoría de los tejidos lavables con agua (etiqueta “W” o “WS”). Elimina la suciedad sin dañar las fibras ni dejar residuos pegajosos. Revive color y textura.
+Fragancia Floral Suave：Deja un aroma floral limpio y sutil, sin olores químicos fuertes. Ideal para el hogar, oficinas y vehículos tras accidentes de mascotas o para un frescor habitual.</t>
+        </is>
+      </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DX2J6DW2?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0HJ99YM29</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -19039,13 +18989,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>58252</v>
+        <v>22869</v>
       </c>
       <c r="P45" s="15">
-        <v>-445</v>
+        <v>-3508</v>
       </c>
       <c r="Q45" s="16">
-        <v>-0.01</v>
+        <v>-0.46</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -19054,55 +19004,61 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T45" s="15">
+        <v>209</v>
+      </c>
+      <c r="U45" s="16">
+        <v>1.04</v>
+      </c>
+      <c r="V45" s="15">
+        <v>3133</v>
+      </c>
+      <c r="W45" s="15" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T45" s="15">
-        <v>42</v>
-      </c>
-      <c r="U45" s="16">
-        <v>-0.14</v>
-      </c>
-      <c r="V45" s="15">
-        <v>3360</v>
-      </c>
-      <c r="W45" s="15"/>
-      <c r="X45" s="15"/>
+      <c r="X45" s="15">
+        <v>750</v>
+      </c>
       <c r="Y45" s="19">
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>79.99</v>
+        <v>14.99</v>
       </c>
       <c r="AA45" s="4"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="19">
-        <v>4789</v>
+        <v>173</v>
       </c>
       <c r="AE45" s="15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.8095</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="20">
-        <v>8.37</v>
+        <v>4.27</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>1239</v>
+        <v>431</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -19116,11 +19072,11 @@
         <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
@@ -19128,9 +19084,21 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU45" s="13"/>
-      <c r="AV45" s="14"/>
-      <c r="AW45" s="13"/>
+      <c r="AU45" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV45" s="14" t="inlineStr">
+        <is>
+          <t>Tin Hau Hong Kong 852 HK</t>
+        </is>
+      </c>
+      <c r="AW45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+        </is>
+      </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13" t="inlineStr">
         <is>
@@ -19145,17 +19113,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD45" s="13"/>
       <c r="BE45" s="13"/>
-      <c r="BF45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
       <c r="BI45" s="23" t="inlineStr">
@@ -19165,43 +19125,43 @@
       </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>3,4 Kilogramos</t>
+          <t>1,1 Kilogramos</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
+          <t>1.10 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>15f. x 28,5an. x 26,5al. centímetros</t>
+          <t>15f. x 27an. x 28al. centímetros</t>
         </is>
       </c>
       <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>1.12 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>1.12 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 34.2 x 19.5 cm</t>
+          <t>24 x 8.3 x 7.7 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 34.20 x 19.50 cm</t>
+          <t>24.00 x 8.30 x 7.70 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -19212,56 +19172,56 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0DX2J6DW2</t>
+          <t>B0DSC6DRWW</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Set name: 1L solución de limpieza</t>
+          <t>Tamaño: 600W | 13kPa Blau</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Marca: Akitas | Color: Azul | Peso del producto: 1,1 Kilogramos | Dimensiones del producto: 15f. x 27an. x 28al. centímetros | Estilo: Compacto | Nombre del modelo: X7 | Capacidad: 1 litros | Fuente de alimentación: Cable eléctrico | Número de unidades: 1000.0 Millilitros | Fabricante: Akitas</t>
+          <t>Marca: CLEANmaxx | Color: Azul | Dimensiones del producto: 30,5f. x 26,5an. x 33al. centímetros | Estilo: Pro Power 600W Azul | Nombre del modelo: Waschsauger | Capacidad: 850 ml | Fuente de alimentación: Cable eléctrico | Número de unidades: 1.0 Conteo | Fabricante: DS Produkte GmbH | Número de productos: 1</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>CLEANmaxx</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Akitas Limpiador para Moquetas y Tapicerías 1L Baja Espuma Fragancia Floral Para Alfombras Sofás Asientos de Coche Elimina Olores y Manchas de Mascotas</t>
+          <t>CLEANmaxx Limpiador de tapicería Pro Power, 600 W, color azul, potente aspiradora de lavado con doble depósito y autolimpieza, ideal para tapicería de sofá, coche, alfombra, fuerte eliminación de</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>Limpieza Profunda de Manchas y Olores：Fórmula profesional que elimina manchas difíciles de mascotas, restos de comida y olores incrustados en alfombras, sofás, moquetas, tapicerías y asientos de coche. Restaura la frescura original.
-Ultra Concentrado 1:25：1L rinde para 25L de solución. Solo diluye 1 parte del producto con 25 partes de agua. Máxima eficiencia y ahorro para limpiezas grandes o frecuentes.
-Baja Espuma y Seguro para Máquinas：Diseñado con fórmula de baja espuma para evitar exceso de burbujas. Compatible con todas las máquinas limpiadoras de alfombras. Seguro para el equipo y fácil de enjuagar.
-Suave con los Tejidos, Fuerte con la Suciedad：Apto para la mayoría de los tejidos lavables con agua (etiqueta “W” o “WS”). Elimina la suciedad sin dañar las fibras ni dejar residuos pegajosos. Revive color y textura.
-Fragancia Floral Suave：Deja un aroma floral limpio y sutil, sin olores químicos fuertes. Ideal para el hogar, oficinas y vehículos tras accidentes de mascotas o para un frescor habitual.</t>
+          <t>Fibras y fondo: el limpiador de alfombras y tapicería CLEANmaxx Pro Power es un profesional fiable de las manchas gracias a su potencia de succión de 600 W y 13 kPa. Con la aspiradora húmeda lograrás resultados limpios incluso en manchas fuertes en alfombras, colchones y escaleras. También ideal para tapicería, felpudos, etc.
+Para todo el hogar: por fin casi todas las alfombras se liberan cómodamente de las manchas y la suciedad más difíciles – sin molestos agacharse ni dolores de espalda. Ya sea en el pasillo, en la sala de estar o en la habitación de los niños: impurezas como café, zumo, vino y huellas húmedas no tienen ninguna oportunidad con este quitamanchas
+Pulverizar, cepillar y aspirar: con este limpiador de manchas siempre utilizarás la cantidad perfecta de agua para limpiar y realizar 3 pasos en una sola operación: lavar, limpiar y aspirar. Para ello, el aspirador tiene una función de autolimpieza. Tan simple, inteligente, ahorra tiempo y limpia la limpieza
+Accesorios inteligentes: utiliza el lado sin escobillas de la boquilla 2 en 1 para espacios más débiles, el lado del cepillo para manchas fuertes, incluso en grietas estrechas. La boquilla combinada con cepillo es ideal para la suciedad persistente, mientras que la boquilla combinada XL tiene un área de limpieza extragrande.
+Flexible y cómodo: mientras que el cable de 5 m y la manguera de 1,2 m garantizan flexibilidad, el sistema de doble tanque garantiza la separación del agua sucia y fresca siempre limpia gracias al depósito de agua sucia (850 ml) y el depósito de agua dulce (1,5 l). Incluye accesorio de goma intercambiable para pelo de animales, pelusas y más.</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DX2J6DW2?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DSC6DRWW?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41-sB8X-Z6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0HJ99YM29</t>
+          <t>B0H8J91VB1</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -19275,13 +19235,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>22869</v>
+        <v>49924</v>
       </c>
       <c r="P46" s="15">
-        <v>-3508</v>
+        <v>127831</v>
       </c>
       <c r="Q46" s="16">
-        <v>-0.46</v>
+        <v>0.77</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -19290,61 +19250,55 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>209</v>
+        <v>42</v>
       </c>
       <c r="U46" s="16">
-        <v>1.04</v>
+        <v>5.67</v>
       </c>
       <c r="V46" s="15">
-        <v>3133</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>750</v>
-      </c>
+        <v>3024</v>
+      </c>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z46" s="20">
-        <v>14.99</v>
+        <v>71.99</v>
       </c>
       <c r="AA46" s="4"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="AE46" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AG46" s="22">
-        <v>0</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="AH46" s="20">
-        <v>4.27</v>
+        <v>9.06</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>431</v>
+        <v>627</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
@@ -19354,15 +19308,13 @@
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46" s="20"/>
-      <c r="AQ46" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ46" s="19"/>
       <c r="AR46" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>DS e-Sales GmbH</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
@@ -19372,82 +19324,70 @@
       </c>
       <c r="AU46" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
+          <t>Stapelfeld 22145 DE</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC46" s="13"/>
       <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Opción Amazon</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>1,1 Kilogramos</t>
+          <t>4,78 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>4.78 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>15f. x 27an. x 28al. centímetros</t>
+          <t>30,5f. x 26,5an. x 33al. centímetros</t>
         </is>
       </c>
       <c r="BM46" s="23"/>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>1.12 kg</t>
+          <t>4.78 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>1.12 kg</t>
+          <t>4.78 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>24 x 8.3 x 7.7 cm</t>
+          <t>37 x 35 x 28.5 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>24.00 x 8.30 x 7.70 cm</t>
+          <t>37.00 x 35.00 x 28.50 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -19458,261 +19398,35 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0DSC6DRWW</t>
+          <t>B0H9PTVK8F</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>Tamaño: 600W | 13kPa Blau</t>
+          <t>Color: White</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>Marca: CLEANmaxx | Color: Azul | Dimensiones del producto: 30,5f. x 26,5an. x 33al. centímetros | Estilo: Pro Power 600W Azul | Nombre del modelo: Waschsauger | Capacidad: 850 ml | Fuente de alimentación: Cable eléctrico | Número de unidades: 1.0 Conteo | Fabricante: DS Produkte GmbH | Número de productos: 1</t>
+          <t>Marca: PUREBEAR | Color: White | Peso del producto: 3,26 Kilogramos | Capacidad: 1250 ml | Número de unidades: 1.0 Conteo | Fabricante: purebear | Número de productos: 1 | Destacado del artículo: Sofás, Alfombras y Colchones| Motor 500W Succión 18kPa| Depósitos Dobles| Cepillos Multiusos| Profunda Manchas Hogar Coche</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx</t>
+          <t>PUREBEAR</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx</t>
+          <t>https://www.amazon.es/stores/Respuestar%C3%A1pidaen24horas/page/E9B73071-F038-4416-BC9B-3CBCC33B0E9B?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>CLEANmaxx Limpiador de tapicería Pro Power, 600 W, color azul, potente aspiradora de lavado con doble depósito y autolimpieza, ideal para tapicería de sofá, coche, alfombra, fuerte eliminación de</t>
+          <t>PUREBEAR Limpiador de manchas portátil con boquilla de autolimpieza</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>Fibras y fondo: el limpiador de alfombras y tapicería CLEANmaxx Pro Power es un profesional fiable de las manchas gracias a su potencia de succión de 600 W y 13 kPa. Con la aspiradora húmeda lograrás resultados limpios incluso en manchas fuertes en alfombras, colchones y escaleras. También ideal para tapicería, felpudos, etc.
-Para todo el hogar: por fin casi todas las alfombras se liberan cómodamente de las manchas y la suciedad más difíciles – sin molestos agacharse ni dolores de espalda. Ya sea en el pasillo, en la sala de estar o en la habitación de los niños: impurezas como café, zumo, vino y huellas húmedas no tienen ninguna oportunidad con este quitamanchas
-Pulverizar, cepillar y aspirar: con este limpiador de manchas siempre utilizarás la cantidad perfecta de agua para limpiar y realizar 3 pasos en una sola operación: lavar, limpiar y aspirar. Para ello, el aspirador tiene una función de autolimpieza. Tan simple, inteligente, ahorra tiempo y limpia la limpieza
-Accesorios inteligentes: utiliza el lado sin escobillas de la boquilla 2 en 1 para espacios más débiles, el lado del cepillo para manchas fuertes, incluso en grietas estrechas. La boquilla combinada con cepillo es ideal para la suciedad persistente, mientras que la boquilla combinada XL tiene un área de limpieza extragrande.
-Flexible y cómodo: mientras que el cable de 5 m y la manguera de 1,2 m garantizan flexibilidad, el sistema de doble tanque garantiza la separación del agua sucia y fresca siempre limpia gracias al depósito de agua sucia (850 ml) y el depósito de agua dulce (1,5 l). Incluye accesorio de goma intercambiable para pelo de animales, pelusas y más.</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0DSC6DRWW?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41-sB8X-Z6L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="14" t="inlineStr">
-        <is>
-          <t>B0H8J91VB1</t>
-        </is>
-      </c>
-      <c r="M47" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O47" s="15">
-        <v>49924</v>
-      </c>
-      <c r="P47" s="15">
-        <v>127831</v>
-      </c>
-      <c r="Q47" s="16">
-        <v>0.77</v>
-      </c>
-      <c r="R47" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="S47" s="18" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="T47" s="15">
-        <v>42</v>
-      </c>
-      <c r="U47" s="16">
-        <v>5.67</v>
-      </c>
-      <c r="V47" s="15">
-        <v>3024</v>
-      </c>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
-      <c r="Y47" s="19">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="20">
-        <v>71.99</v>
-      </c>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="15"/>
-      <c r="AD47" s="19">
-        <v>59</v>
-      </c>
-      <c r="AE47" s="15">
-        <v>3</v>
-      </c>
-      <c r="AF47" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG47" s="22">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="AH47" s="20">
-        <v>9.06</v>
-      </c>
-      <c r="AI47" s="16">
-        <v>0.73</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="AL47" s="19">
-        <v>627</v>
-      </c>
-      <c r="AM47" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN47" s="13"/>
-      <c r="AO47" s="13"/>
-      <c r="AP47" s="20"/>
-      <c r="AQ47" s="19"/>
-      <c r="AR47" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS47" s="14" t="inlineStr">
-        <is>
-          <t>DS e-Sales GmbH</t>
-        </is>
-      </c>
-      <c r="AT47" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>Stapelfeld 22145 DE</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K</t>
-        </is>
-      </c>
-      <c r="AX47" s="13"/>
-      <c r="AY47" s="13"/>
-      <c r="AZ47" s="13"/>
-      <c r="BA47" s="13"/>
-      <c r="BB47" s="13"/>
-      <c r="BC47" s="13"/>
-      <c r="BD47" s="13"/>
-      <c r="BE47" s="13"/>
-      <c r="BF47" s="13"/>
-      <c r="BG47" s="13"/>
-      <c r="BH47" s="14"/>
-      <c r="BI47" s="23"/>
-      <c r="BJ47" s="23" t="inlineStr">
-        <is>
-          <t>4,78 kg</t>
-        </is>
-      </c>
-      <c r="BK47" s="23" t="inlineStr">
-        <is>
-          <t>4.78 kg</t>
-        </is>
-      </c>
-      <c r="BL47" s="23" t="inlineStr">
-        <is>
-          <t>30,5f. x 26,5an. x 33al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>4.78 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>4.78 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>37 x 35 x 28.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>37.00 x 35.00 x 28.50 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
-        <v>47</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>B0H9PTVK8F</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>Color: White</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Marca: PUREBEAR | Color: White | Peso del producto: 3,26 Kilogramos | Capacidad: 1250 ml | Número de unidades: 1.0 Conteo | Fabricante: purebear | Número de productos: 1 | Destacado del artículo: Sofás, Alfombras y Colchones| Motor 500W Succión 18kPa| Depósitos Dobles| Cepillos Multiusos| Profunda Manchas Hogar Coche</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/stores/Respuestar%C3%A1pidaen24horas/page/E9B73071-F038-4416-BC9B-3CBCC33B0E9B?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR Limpiador de manchas portátil con boquilla de autolimpieza</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>COMPACTO, PORTÁTIL Y FÁCIL DE GUARDAR: Su diseño compacto permite transportarlo fácilmente de una habitación a otra o utilizarlo para limpiar el coche. Ideal para tratar derrames, manchas de comida, suciedad diaria y pequeños accidentes en diferentes superficies textiles.
 2 CEPILLOS PARA DIFERENTES SUPERFICIES: Incluye dos cabezales de limpieza para adaptarse a distintas necesidades. Utiliza el cepillo adecuado para limpiar manchas en sofás, alfombras, escaleras, colchones, tapicerías y el interior del coche con mayor comodidad.
@@ -19721,236 +19435,236 @@
 LIMPIEZA PROFUNDA CON 18 kPa DE SUCCIÓN: El potente motor de 500 W proporciona hasta 18 kPa de succión para ayudar a eliminar manchas y suciedad de sofás, alfombras, tapicerías, colchones, asientos de coche y otras superficies textiles. Una solución práctica para la limpieza diaria de manchas en casa.</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.es/dp/B0H9PTVK8F?psc=1</t>
         </is>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="K47" s="14" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L48" s="14" t="inlineStr">
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>B0HKMLWTQ6</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr">
+      <c r="M47" s="14" t="inlineStr">
         <is>
           <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
         </is>
       </c>
-      <c r="N48" s="14" t="inlineStr">
+      <c r="N47" s="14" t="inlineStr">
         <is>
           <t>Hogar y cocina</t>
         </is>
       </c>
-      <c r="O48" s="15">
+      <c r="O47" s="15">
         <v>13312</v>
       </c>
-      <c r="P48" s="15">
+      <c r="P47" s="15">
         <v>37492</v>
       </c>
-      <c r="Q48" s="16">
+      <c r="Q47" s="16">
         <v>0.48</v>
       </c>
-      <c r="R48" s="17" t="inlineStr">
+      <c r="R47" s="17" t="inlineStr">
         <is>
           <t>Aspiradoras para alfombras</t>
         </is>
       </c>
-      <c r="S48" s="18" t="inlineStr">
+      <c r="S47" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="T48" s="15">
+      <c r="T47" s="15">
         <v>19</v>
       </c>
-      <c r="U48" s="16"/>
-      <c r="V48" s="15">
+      <c r="U47" s="16"/>
+      <c r="V47" s="15">
         <v>2012</v>
       </c>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
-      <c r="Y48" s="19">
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
+      <c r="Y47" s="19">
         <v>1</v>
       </c>
-      <c r="Z48" s="20">
+      <c r="Z47" s="20">
         <v>105.87</v>
       </c>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="1"/>
-      <c r="AC48" s="15"/>
-      <c r="AD48" s="19">
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="15"/>
+      <c r="AD47" s="19">
         <v>40</v>
       </c>
-      <c r="AE48" s="15">
+      <c r="AE47" s="15">
         <v>0</v>
       </c>
-      <c r="AF48" s="21">
+      <c r="AF47" s="21">
         <v>4.6</v>
       </c>
-      <c r="AG48" s="22">
+      <c r="AG47" s="22">
         <v>0</v>
       </c>
-      <c r="AH48" s="20">
+      <c r="AH47" s="20">
         <v>8.72</v>
       </c>
-      <c r="AI48" s="16">
+      <c r="AI47" s="16">
         <v>0.78</v>
       </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="13" t="inlineStr">
+      <c r="AJ47"/>
+      <c r="AK47" s="13" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AL48" s="19">
+      <c r="AL47" s="19">
         <v>9</v>
       </c>
-      <c r="AM48" s="13" t="inlineStr">
+      <c r="AM47" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN48" s="13"/>
-      <c r="AO48" s="13"/>
-      <c r="AP48" s="20"/>
-      <c r="AQ48" s="19">
+      <c r="AN47" s="13"/>
+      <c r="AO47" s="13"/>
+      <c r="AP47" s="20"/>
+      <c r="AQ47" s="19">
         <v>10</v>
       </c>
-      <c r="AR48" s="19">
+      <c r="AR47" s="19">
         <v>1</v>
       </c>
-      <c r="AS48" s="14" t="inlineStr">
+      <c r="AS47" s="14" t="inlineStr">
         <is>
           <t>MengfanchaoMLw</t>
         </is>
       </c>
-      <c r="AT48" s="13" t="inlineStr">
+      <c r="AT47" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU48" s="13" t="inlineStr">
+      <c r="AU47" s="13" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AV48" s="14" t="inlineStr">
+      <c r="AV47" s="14" t="inlineStr">
         <is>
           <t>huanggangshi hubeisheng 438000 CN</t>
         </is>
       </c>
-      <c r="AW48" s="13" t="inlineStr">
+      <c r="AW47" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
         </is>
       </c>
-      <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
+      <c r="AX47" s="13"/>
+      <c r="AY47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ48" s="13"/>
-      <c r="BA48" s="13"/>
-      <c r="BB48" s="13"/>
-      <c r="BC48" s="13" t="inlineStr">
+      <c r="AZ47" s="13"/>
+      <c r="BA47" s="13"/>
+      <c r="BB47" s="13"/>
+      <c r="BC47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD48" s="13" t="inlineStr">
+      <c r="BD47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE48" s="13"/>
-      <c r="BF48" s="13" t="inlineStr">
+      <c r="BE47" s="13"/>
+      <c r="BF47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG48" s="13"/>
-      <c r="BH48" s="14"/>
-      <c r="BI48" s="23" t="inlineStr">
+      <c r="BG47" s="13"/>
+      <c r="BH47" s="14"/>
+      <c r="BI47" s="23" t="inlineStr">
         <is>
           <t>Opción Amazon</t>
         </is>
       </c>
-      <c r="BJ48" s="23" t="inlineStr">
+      <c r="BJ47" s="23" t="inlineStr">
         <is>
           <t>3,26 Kilogramos</t>
         </is>
       </c>
-      <c r="BK48" s="23" t="inlineStr">
+      <c r="BK47" s="23" t="inlineStr">
         <is>
           <t>3.26 kg</t>
         </is>
       </c>
-      <c r="BL48" s="23"/>
-      <c r="BM48" s="23"/>
-      <c r="BN48" s="23" t="inlineStr">
+      <c r="BL47" s="23"/>
+      <c r="BM47" s="23"/>
+      <c r="BN47" s="23" t="inlineStr">
         <is>
           <t>4.39 kg</t>
         </is>
       </c>
-      <c r="BO48" s="23" t="inlineStr">
+      <c r="BO47" s="23" t="inlineStr">
         <is>
           <t>4.39 kg</t>
         </is>
       </c>
-      <c r="BP48" s="23" t="inlineStr">
+      <c r="BP47" s="23" t="inlineStr">
         <is>
           <t>44.5 x 35.2 x 20.3 cm</t>
         </is>
       </c>
-      <c r="BQ48" s="23" t="inlineStr">
+      <c r="BQ47" s="23" t="inlineStr">
         <is>
           <t>44.50 x 35.20 x 20.30 cm</t>
         </is>
       </c>
-      <c r="BR48" s="13" t="inlineStr">
+      <c r="BR47" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="13">
-        <v>48</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14" t="inlineStr">
+    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
+        <v>47</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>B0FNRQFHWC</t>
         </is>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="D48" s="14"/>
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>Marca: Shark | Color: Blanco Con Detalles En Negro | Peso del producto: 3,46 Kilogramos | Dimensiones del producto: 9,6f. x 6,8an. x 50,4al. centímetros | Estilo: StainForce | Nombre del modelo: Spot Cleaning | Fuente de alimentación: Funciona con batería | Fabricante: Shark | UPC: 622356320221 | Número de productos: 1</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>Shark</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.es/stores/SharkINinja/page/A7BF4C0E-A1DC-446C-A093-0732B0FC27D7?lp_asin=B0FNRQFHWC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>Shark StainForce, Eliminación de manchas y olores en alfombras, moquetas, tapicería, escaleras y coches, diseño ligero y portátil con organizador, accesorios y solución de limpieza total, HX100EUT</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>SISTEMA DESTRUCTOR DE MANCHAS SIN CABLE: El limpiador de manchas destruye al instante cualquier mancha que se detecte*
 30 VECES MÁS PODER ANTIMANCHAS: Las fórmulas antimanchas más potentes de Shark se mezclan y activan cuando entran en contacto para eliminar las manchas más difíciles**
@@ -19959,19 +19673,251 @@
 PARA SOLUCIONAR AL INSTANTE VERTIDOS Y MANCHAS INCRUSTADAS*: Limpiador de manchas portátil diseñado para usar en alfombras, moquetas, escaleras, tapicería, interiores de coches y más****</t>
         </is>
       </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/dp/B0FNRQFHWC?psc=1</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
+          <t>B0FNRQFHWC</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
+        </is>
+      </c>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>Hogar y cocina</t>
+        </is>
+      </c>
+      <c r="O48" s="15">
+        <v>55259</v>
+      </c>
+      <c r="P48" s="15">
+        <v>136433</v>
+      </c>
+      <c r="Q48" s="16">
+        <v>0.55</v>
+      </c>
+      <c r="R48" s="17" t="inlineStr">
+        <is>
+          <t>Aspiradoras para alfombras</t>
+        </is>
+      </c>
+      <c r="S48" s="18" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="T48" s="15">
+        <v>6</v>
+      </c>
+      <c r="U48" s="16"/>
+      <c r="V48" s="15">
+        <v>894</v>
+      </c>
+      <c r="W48" s="15"/>
+      <c r="X48" s="15"/>
+      <c r="Y48" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="20">
+        <v>156.64</v>
+      </c>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="15"/>
+      <c r="AD48" s="19">
+        <v>4</v>
+      </c>
+      <c r="AE48" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="21">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="20">
+        <v>7.35</v>
+      </c>
+      <c r="AI48" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="AJ48"/>
+      <c r="AK48" s="13" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AL48" s="19">
+        <v>340</v>
+      </c>
+      <c r="AM48" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN48" s="13"/>
+      <c r="AO48" s="13"/>
+      <c r="AP48" s="20"/>
+      <c r="AQ48" s="19"/>
+      <c r="AR48" s="19">
+        <v>3</v>
+      </c>
+      <c r="AS48" s="14" t="inlineStr">
+        <is>
+          <t>PACIJO</t>
+        </is>
+      </c>
+      <c r="AT48" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU48" s="13" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="AV48" s="14" t="inlineStr">
+        <is>
+          <t>Setúbal 2870-803 PT</t>
+        </is>
+      </c>
+      <c r="AW48" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JJI37K279DYY</t>
+        </is>
+      </c>
+      <c r="AX48" s="13"/>
+      <c r="AY48" s="13"/>
+      <c r="AZ48" s="13"/>
+      <c r="BA48" s="13"/>
+      <c r="BB48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD48" s="13"/>
+      <c r="BE48" s="13"/>
+      <c r="BF48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG48" s="13"/>
+      <c r="BH48" s="14"/>
+      <c r="BI48" s="23"/>
+      <c r="BJ48" s="23" t="inlineStr">
+        <is>
+          <t>3,46 Kilogramos</t>
+        </is>
+      </c>
+      <c r="BK48" s="23" t="inlineStr">
+        <is>
+          <t>3.46 kg</t>
+        </is>
+      </c>
+      <c r="BL48" s="23" t="inlineStr">
+        <is>
+          <t>9,6f. x 6,8an. x 50,4al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM48" s="23"/>
+      <c r="BN48" s="23" t="inlineStr">
+        <is>
+          <t>4.83 kg</t>
+        </is>
+      </c>
+      <c r="BO48" s="23" t="inlineStr">
+        <is>
+          <t>4.83 kg</t>
+        </is>
+      </c>
+      <c r="BP48" s="23" t="inlineStr">
+        <is>
+          <t>44 x 28.5 x 26 cm</t>
+        </is>
+      </c>
+      <c r="BQ48" s="23" t="inlineStr">
+        <is>
+          <t>44.00 x 28.50 x 26.00 cm</t>
+        </is>
+      </c>
+      <c r="BR48" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>48</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>B0HBCB6GRG</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Color: Gris</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Marca: Circlio | Función especial: ① Motor sin escobillas de 600 W ② Potente succión de 58 Kpa ③ Hasta 75 minutos de autonomía en modo Eco. ④ Depósito de polvo de gran capacidad de 1,6 L ⑤ Baterías extraíbles de 8*3200 mAh ⑥ Filtración eficaz del 99,99 % ⑦ Pantalla LED táctil inteligente con recordatorio de limpieza del cepillo motorizado y del depósito de polvo ⑧ Cepillo en forma de V anti-enredos ⑨ Soporte de pared para carga y almacenamiento ⑩ Servicio de atención al cliente confiable | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra/Baldosas de Cerámica/Electrónica/Hormigón/Laminado/Linóleo/Maderas Duras/Suelo duro/Tapicería/Todos los suelos | Fuente de alimentación: Batería | Voltaje: 28,8 Voltios | Componentes incluidos: ➤ 1 × Aspiradora Circlio ➤ 1 × Batería de 92,16Wh (Celda de 3,7V 3200mAh) ➤ 1 × Desenredador de Pelo de Mascotas ➤ 1 × Cortapelos eléctrico ➤ 1 × Soporte de pared ➤ 1 × Cepillo largo para rincones ➤ 1 × Cepillo 2 en 1 ➤ 2 × Filtros HEPA (MiF) ➤ 1 × Adaptador ➤ 1 × Mini cepillo de limpieza ➤ 1 × Guía rápida de inicio ➤ 1 × Manual de usuario ➤ 1 × Motor principal ➤ 1 × Tubo telescópico ➤ 1 × Cepillo para suelos con luz LED ➤ 1 × Depósito de polvo ➤ 1 × Rodillo en forma de V | ¿Es inalámbrico?: Sí | Peso del producto: 4 Kilogramos | Capacidad: 1,6 litros</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Circlio</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>Aspiradora sin Cable 58Kpa/600W/75Min para Suelos/Alfombras/Pelo de Animale</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>【58.000 Pa de Potencia de Succión &amp; Motor Silencioso de 600 W】 El aspirador sin cable NOVAX T80 Sense combina un potente motor Brushless de 600 W con una potencia de succión de hasta 58.000 Pa. Elimina eficazmente pelos de mascotas, polvo fino y suciedad incrustada tanto en suelos duros como en alfombras. Con un nivel de ruido inferior a 62 dB, ofrece una limpieza potente y agradablemente silenciosa.
+【Hasta 75 Min de Autonomía &amp; Carga Automática】 La batería de alta capacidad ofrece hasta 75 minutos de autonomía en modo Auto y se carga completamente en solo 2,5 horas. Basta con colocar la escoba aspiradora sin cable en el soporte de pared para que la carga se inicie automáticamente, sin necesidad de conectar el cable manualmente. Los accesorios también pueden guardarse cómodamente en la propia estación.
+【Detección Inteligente de Polvo &amp; 4 Modos de Succión】 En modo Auto, el T80 Sense detecta en tiempo real la cantidad de polvo y ajusta automáticamente la potencia de succión, con una autonomía aproximada de 25–75 minutos. También dispone de los modos Floor (60 min), Carpet (30 min) y Turbo (18 min). La pantalla LED muestra claramente el nivel de batería, el modo seleccionado y los avisos de mantenimiento. Una aspiradora sin cable diseñada para adaptar su rendimiento a cada tipo de limpieza.
+【Filtración HEPA de 6 Etapas &amp; Depósito de 1,6 L】 El sistema de filtración multicapa con doble filtro HEPA y filtro MIF captura el 99,99 % de las partículas finas y alérgenos de hasta 0,3 µm. El amplio depósito de 1,6 L reduce la frecuencia de vaciado y puede vaciarse de forma higiénica con una sola mano y pulsando un botón. Este aspirador vertical combina una filtración eficiente con un mantenimiento sencillo.
+【Diseño Autoportante &amp; Garantía de 2+1 Años】 Gracias a su diseño autoportante, el T80 Sense puede mantenerse de pie de forma estable en cualquier momento durante la limpieza, sin necesidad de apoyarlo en la pared. Este vacuum cleaner combina potencia, autonomía y comodidad para facilitar la limpieza diaria. Además, incluye una garantía del fabricante de 2+1 años tras el registro y servicio de atención al cliente gratuito para consultas sobre uso, accesorios o asistencia técnica.</t>
+        </is>
+      </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FNRQFHWC?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HBCB6GRG?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FNRQFHWC</t>
+          <t>B0HKJPHGRM</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -19985,13 +19931,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>55259</v>
+        <v>20836</v>
       </c>
       <c r="P49" s="15">
-        <v>136433</v>
+        <v>332380</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -20000,15 +19946,15 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U49" s="16"/>
       <c r="V49" s="15">
-        <v>894</v>
+        <v>480</v>
       </c>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
@@ -20016,37 +19962,37 @@
         <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>156.64</v>
+        <v>159.99</v>
       </c>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AE49" s="15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AF49" s="21">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
       <c r="AH49" s="20">
-        <v>7.35</v>
+        <v>6.15</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>340</v>
+        <v>27</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -20056,13 +20002,15 @@
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49" s="20"/>
-      <c r="AQ49" s="19"/>
+      <c r="AQ49" s="19">
+        <v>10</v>
+      </c>
       <c r="AR49" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>PACIJO</t>
+          <t>Zenithor es</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -20072,17 +20020,17 @@
       </c>
       <c r="AU49" s="13" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>Setúbal 2870-803 PT</t>
+          <t>Romania 234555 RO</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JJI37K279DYY</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -20095,50 +20043,50 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13"/>
+      <c r="BD49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE49" s="13"/>
-      <c r="BF49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
       <c r="BI49" s="23"/>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>3,46 Kilogramos</t>
+          <t>4 Kilogramos</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>3.46 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>9,6f. x 6,8an. x 50,4al. centímetros</t>
+          <t>5l. x 5an. x 5al. centímetros</t>
         </is>
       </c>
       <c r="BM49" s="23"/>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>4.83 kg</t>
+          <t>4.18 kg</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>4.83 kg</t>
+          <t>4.18 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>44 x 28.5 x 26 cm</t>
+          <t>43.7 x 33.8 x 18.7 cm</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 28.50 x 26.00 cm</t>
+          <t>43.70 x 33.80 x 18.70 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
@@ -20154,56 +20102,53 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0HBCB6GRG</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Color: Gris</t>
-        </is>
-      </c>
+          <t>B0GNB36YF6</t>
+        </is>
+      </c>
+      <c r="D50" s="14"/>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Marca: Circlio | Función especial: ① Motor sin escobillas de 600 W ② Potente succión de 58 Kpa ③ Hasta 75 minutos de autonomía en modo Eco. ④ Depósito de polvo de gran capacidad de 1,6 L ⑤ Baterías extraíbles de 8*3200 mAh ⑥ Filtración eficaz del 99,99 % ⑦ Pantalla LED táctil inteligente con recordatorio de limpieza del cepillo motorizado y del depósito de polvo ⑧ Cepillo en forma de V anti-enredos ⑨ Soporte de pared para carga y almacenamiento ⑩ Servicio de atención al cliente confiable | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra/Baldosas de Cerámica/Electrónica/Hormigón/Laminado/Linóleo/Maderas Duras/Suelo duro/Tapicería/Todos los suelos | Fuente de alimentación: Batería | Voltaje: 28,8 Voltios | Componentes incluidos: ➤ 1 × Aspiradora Circlio ➤ 1 × Batería de 92,16Wh (Celda de 3,7V 3200mAh) ➤ 1 × Desenredador de Pelo de Mascotas ➤ 1 × Cortapelos eléctrico ➤ 1 × Soporte de pared ➤ 1 × Cepillo largo para rincones ➤ 1 × Cepillo 2 en 1 ➤ 2 × Filtros HEPA (MiF) ➤ 1 × Adaptador ➤ 1 × Mini cepillo de limpieza ➤ 1 × Guía rápida de inicio ➤ 1 × Manual de usuario ➤ 1 × Motor principal ➤ 1 × Tubo telescópico ➤ 1 × Cepillo para suelos con luz LED ➤ 1 × Depósito de polvo ➤ 1 × Rodillo en forma de V | ¿Es inalámbrico?: Sí | Peso del producto: 4 Kilogramos | Capacidad: 1,6 litros</t>
+          <t>Marca: Vonia | Función especial: Ergonómico y Seguridad reforzada | Recomendación de superficie: Piso, Azulejos, Alfombra, Junta, Fregadero, Ventana, Espejo, Textil, Aparato de cocina, Cuarto de baño | Nombre del modelo: Powell 2000W | Componentes incluidos: Almohadilla de microfibra, Deslizador para alfombras, Cepillos especiales para juntas y grifos, Adaptador de accesorios, Vidrio dosificador | Vataje: 2000 vatios | Peso del producto: 3,6 Kilogramos | Volumen del depósito: 1,8 Litros | Factor de forma: Vertical | Tiempo de calentamiento: 20 Segundos</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Circlio</t>
+          <t>Vonia</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.es/stores/Lom%C3%A1simportanteparatuhogar/page/0A2EDD59-3DB7-4014-B2F7-4216ECC1A033?lp_asin=B0GNB36YF6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora sin Cable 58Kpa/600W/75Min para Suelos/Alfombras/Pelo de Animale</t>
+          <t>Powell Vaporeta Limpieza Hogar 2000W, Limpiador a Vapor 5 Bar, Depósito 2 L</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>【58.000 Pa de Potencia de Succión &amp; Motor Silencioso de 600 W】 El aspirador sin cable NOVAX T80 Sense combina un potente motor Brushless de 600 W con una potencia de succión de hasta 58.000 Pa. Elimina eficazmente pelos de mascotas, polvo fino y suciedad incrustada tanto en suelos duros como en alfombras. Con un nivel de ruido inferior a 62 dB, ofrece una limpieza potente y agradablemente silenciosa.
-【Hasta 75 Min de Autonomía &amp; Carga Automática】 La batería de alta capacidad ofrece hasta 75 minutos de autonomía en modo Auto y se carga completamente en solo 2,5 horas. Basta con colocar la escoba aspiradora sin cable en el soporte de pared para que la carga se inicie automáticamente, sin necesidad de conectar el cable manualmente. Los accesorios también pueden guardarse cómodamente en la propia estación.
-【Detección Inteligente de Polvo &amp; 4 Modos de Succión】 En modo Auto, el T80 Sense detecta en tiempo real la cantidad de polvo y ajusta automáticamente la potencia de succión, con una autonomía aproximada de 25–75 minutos. También dispone de los modos Floor (60 min), Carpet (30 min) y Turbo (18 min). La pantalla LED muestra claramente el nivel de batería, el modo seleccionado y los avisos de mantenimiento. Una aspiradora sin cable diseñada para adaptar su rendimiento a cada tipo de limpieza.
-【Filtración HEPA de 6 Etapas &amp; Depósito de 1,6 L】 El sistema de filtración multicapa con doble filtro HEPA y filtro MIF captura el 99,99 % de las partículas finas y alérgenos de hasta 0,3 µm. El amplio depósito de 1,6 L reduce la frecuencia de vaciado y puede vaciarse de forma higiénica con una sola mano y pulsando un botón. Este aspirador vertical combina una filtración eficiente con un mantenimiento sencillo.
-【Diseño Autoportante &amp; Garantía de 2+1 Años】 Gracias a su diseño autoportante, el T80 Sense puede mantenerse de pie de forma estable en cualquier momento durante la limpieza, sin necesidad de apoyarlo en la pared. Este vacuum cleaner combina potencia, autonomía y comodidad para facilitar la limpieza diaria. Además, incluye una garantía del fabricante de 2+1 años tras el registro y servicio de atención al cliente gratuito para consultas sobre uso, accesorios o asistencia técnica.</t>
+          <t>[vapor a 5 bar, solo con agua del grifo] Los 2000 W calientan el agua y generan vapor a presión de hasta 5 bar, que afloja la grasa de la cocina, la cal y la suciedad incrustada en azulejos, juntas y sanitarios. No necesitas detergentes: la vaporeta limpia únicamente con agua, así que no quedan restos de productos químicos en suelos y superficies.
+[depósito de 2 litros: hasta 60 minutos de vapor] Con el depósito lleno puedes limpiar hasta 60 minutos seguidos, suficiente para el baño, la cocina y los suelos de una vivienda sin parar a rellenar. El aparato está listo en unos 60 segundos y un piloto indica cuándo está en funcionamiento. Se incluyen vaso medidor y embudo para rellenarlo sin derramar agua.
+[vapor regulable desde la empuñadura] El caudal de vapor se ajusta de forma continua con el mando de la empuñadura. Usa menos vapor para refrescar tejidos y cristales y el máximo para juntas, encimeras o la placa de cocina, sin tener que agacharte al aparato.
+[accesorios para suelos, juntas y ventanas] Incluye pistola de vapor de mano, tubos alargadores, boquilla para suelos con paño, accesorio para alfombras, limpiacristales con rasqueta, cepillo triangular, cepillo redondo, boquillas de precisión, paños de microfibra, vaso medidor y embudo. Con la pistola y las boquillas llegas a grifos, rincones, marcos de ventana y juntas estrechas.
+[también para alfombras, sofás y tapicería] Con el accesorio deslizante para alfombras y el paño de microfibra refrescas alfombras, moquetas y sofás con vapor. Ten en cuenta que la vaporeta no aspira: afloja la suciedad, pero no extrae agua ni manchas del tejido. Para manchas profundas en tapicería se necesita un limpiador con aspiración.
+[vaporeta de trineo con ruedas y cable de 3 m] El cuerpo pesa 3,6 kg, mide 37 x 26,5 x 24 cm y se desplaza sobre ruedas detrás de ti mientras limpias. El cable de 3 m y la manguera flexible te dan margen de movimiento, y el cable se guarda en el propio aparato. Apta para baldosas, laminado, vinilo y otros suelos duros sellados; prueba primero en una zona poco visible.</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0HBCB6GRG?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GNB36YF6?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41rp9ak74VL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0HKJPHGRM</t>
+          <t>B0GNB36YF6</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -20217,13 +20162,13 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>20836</v>
+        <v>57032</v>
       </c>
       <c r="P50" s="15">
-        <v>332380</v>
+        <v>224592</v>
       </c>
       <c r="Q50" s="16">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="R50" s="17" t="inlineStr">
         <is>
@@ -20232,15 +20177,15 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T50" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U50" s="16"/>
       <c r="V50" s="15">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="W50" s="15"/>
       <c r="X50" s="15"/>
@@ -20248,37 +20193,37 @@
         <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>159.99</v>
+        <v>74.95</v>
       </c>
       <c r="AA50" s="4"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="19">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE50" s="15">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AF50" s="21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
       </c>
       <c r="AH50" s="20">
-        <v>6.15</v>
+        <v>9.75</v>
       </c>
       <c r="AI50" s="16">
-        <v>0.81</v>
+        <v>0.72</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AL50" s="19">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="AM50" s="13" t="inlineStr">
         <is>
@@ -20289,14 +20234,14 @@
       <c r="AO50" s="13"/>
       <c r="AP50" s="20"/>
       <c r="AQ50" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR50" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS50" s="14" t="inlineStr">
         <is>
-          <t>Zenithor es</t>
+          <t>Dennepark B.V</t>
         </is>
       </c>
       <c r="AT50" s="13" t="inlineStr">
@@ -20306,17 +20251,17 @@
       </c>
       <c r="AU50" s="13" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="AV50" s="14" t="inlineStr">
         <is>
-          <t>Romania 234555 RO</t>
+          <t>Zuid-Holland 2497 GC NL</t>
         </is>
       </c>
       <c r="AW50" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08</t>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25QV76UBVZPI4</t>
         </is>
       </c>
       <c r="AX50" s="13"/>
@@ -20324,11 +20269,7 @@
       <c r="AZ50" s="13"/>
       <c r="BA50" s="13"/>
       <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC50" s="13"/>
       <c r="BD50" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20341,268 +20282,41 @@
       <c r="BI50" s="23"/>
       <c r="BJ50" s="23" t="inlineStr">
         <is>
-          <t>4 Kilogramos</t>
+          <t>3,6 Kilogramos</t>
         </is>
       </c>
       <c r="BK50" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>3.60 kg</t>
         </is>
       </c>
       <c r="BL50" s="23" t="inlineStr">
         <is>
-          <t>5l. x 5an. x 5al. centímetros</t>
+          <t>37f. x 26,5an. x 24al. centímetros</t>
         </is>
       </c>
       <c r="BM50" s="23"/>
       <c r="BN50" s="23" t="inlineStr">
         <is>
-          <t>4.18 kg</t>
+          <t>3.6 kg</t>
         </is>
       </c>
       <c r="BO50" s="23" t="inlineStr">
         <is>
-          <t>4.18 kg</t>
+          <t>3.60 kg</t>
         </is>
       </c>
       <c r="BP50" s="23" t="inlineStr">
         <is>
-          <t>43.7 x 33.8 x 18.7 cm</t>
+          <t>47 x 33.5 x 31.2 cm</t>
         </is>
       </c>
       <c r="BQ50" s="23" t="inlineStr">
         <is>
-          <t>43.70 x 33.80 x 18.70 cm</t>
+          <t>47.00 x 33.50 x 31.20 cm</t>
         </is>
       </c>
       <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0GNB36YF6</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Marca: Vonia | Función especial: Ergonómico y Seguridad reforzada | Recomendación de superficie: Piso, Azulejos, Alfombra, Junta, Fregadero, Ventana, Espejo, Textil, Aparato de cocina, Cuarto de baño | Nombre del modelo: Powell 2000W | Componentes incluidos: Almohadilla de microfibra, Deslizador para alfombras, Cepillos especiales para juntas y grifos, Adaptador de accesorios, Vidrio dosificador | Vataje: 2000 vatios | Peso del producto: 3,6 Kilogramos | Volumen del depósito: 1,8 Litros | Factor de forma: Vertical | Tiempo de calentamiento: 20 Segundos</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Vonia</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/stores/Lom%C3%A1simportanteparatuhogar/page/0A2EDD59-3DB7-4014-B2F7-4216ECC1A033?lp_asin=B0GNB36YF6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Powell Vaporeta Limpieza Hogar 2000W, Limpiador a Vapor 5 Bar, Depósito 2 L</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>[vapor a 5 bar, solo con agua del grifo] Los 2000 W calientan el agua y generan vapor a presión de hasta 5 bar, que afloja la grasa de la cocina, la cal y la suciedad incrustada en azulejos, juntas y sanitarios. No necesitas detergentes: la vaporeta limpia únicamente con agua, así que no quedan restos de productos químicos en suelos y superficies.
-[depósito de 2 litros: hasta 60 minutos de vapor] Con el depósito lleno puedes limpiar hasta 60 minutos seguidos, suficiente para el baño, la cocina y los suelos de una vivienda sin parar a rellenar. El aparato está listo en unos 60 segundos y un piloto indica cuándo está en funcionamiento. Se incluyen vaso medidor y embudo para rellenarlo sin derramar agua.
-[vapor regulable desde la empuñadura] El caudal de vapor se ajusta de forma continua con el mando de la empuñadura. Usa menos vapor para refrescar tejidos y cristales y el máximo para juntas, encimeras o la placa de cocina, sin tener que agacharte al aparato.
-[accesorios para suelos, juntas y ventanas] Incluye pistola de vapor de mano, tubos alargadores, boquilla para suelos con paño, accesorio para alfombras, limpiacristales con rasqueta, cepillo triangular, cepillo redondo, boquillas de precisión, paños de microfibra, vaso medidor y embudo. Con la pistola y las boquillas llegas a grifos, rincones, marcos de ventana y juntas estrechas.
-[también para alfombras, sofás y tapicería] Con el accesorio deslizante para alfombras y el paño de microfibra refrescas alfombras, moquetas y sofás con vapor. Ten en cuenta que la vaporeta no aspira: afloja la suciedad, pero no extrae agua ni manchas del tejido. Para manchas profundas en tapicería se necesita un limpiador con aspiración.
-[vaporeta de trineo con ruedas y cable de 3 m] El cuerpo pesa 3,6 kg, mide 37 x 26,5 x 24 cm y se desplaza sobre ruedas detrás de ti mientras limpias. El cable de 3 m y la manguera flexible te dan margen de movimiento, y el cable se guarda en el propio aparato. Apta para baldosas, laminado, vinilo y otros suelos duros sellados; prueba primero en una zona poco visible.</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0GNB36YF6?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41rp9ak74VL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0GNB36YF6</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>57032</v>
-      </c>
-      <c r="P51" s="15">
-        <v>224592</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.69</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras para alfombras</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>6</v>
-      </c>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15">
-        <v>450</v>
-      </c>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>74.95</v>
-      </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>11</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>9.75</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.72</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>219</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="20"/>
-      <c r="AQ51" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Dennepark B.V</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>Zuid-Holland 2497 GC NL</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25QV76UBVZPI4</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>3,6 Kilogramos</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>3.60 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>37f. x 26,5an. x 24al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>3.6 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>3.60 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>47 x 33.5 x 31.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>47.00 x 33.50 x 31.20 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
@@ -20903,86 +20617,79 @@
     <hyperlink ref="M41" r:id="rId289" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N41" r:id="rId290"/>
     <hyperlink ref="AW41" r:id="rId291" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
-    <hyperlink ref="C42" r:id="rId292" tooltip="https://www.amazon.es/dp/B0DDPL3PD2"/>
-    <hyperlink ref="G42" r:id="rId293" tooltip="https://www.amazon.es/stores/Vacmaster/page/935EC746-F3AD-4C28-9B32-85256EBEE494?lp_asin=B0DDPL3PD2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId294" tooltip="https://www.amazon.es/dp/B0DDPL3PD2?psc=1"/>
-    <hyperlink ref="K42" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/61chaSQ+1CL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId296" tooltip="https://www.amazon.es/dp/B0HJHD1BWJ"/>
+    <hyperlink ref="C42" r:id="rId292" tooltip="https://www.amazon.es/dp/B08KXVXC82"/>
+    <hyperlink ref="G42" r:id="rId293" tooltip="https://www.amazon.es/stores/MEDION/page/674A7F5D-6984-42A5-8C9C-550514A9CEDC?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId294" tooltip="https://www.amazon.es/dp/B08KXVXC82?psc=1"/>
+    <hyperlink ref="K42" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId296" tooltip="https://www.amazon.es/dp/B08KXVXC82"/>
     <hyperlink ref="M42" r:id="rId297" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N42" r:id="rId298"/>
-    <hyperlink ref="C43" r:id="rId299" tooltip="https://www.amazon.es/dp/B08KXVXC82"/>
-    <hyperlink ref="G43" r:id="rId300" tooltip="https://www.amazon.es/stores/MEDION/page/674A7F5D-6984-42A5-8C9C-550514A9CEDC?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId301" tooltip="https://www.amazon.es/dp/B08KXVXC82?psc=1"/>
-    <hyperlink ref="K43" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId303" tooltip="https://www.amazon.es/dp/B08KXVXC82"/>
-    <hyperlink ref="M43" r:id="rId304" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N43" r:id="rId305"/>
-    <hyperlink ref="AW43" r:id="rId306" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
-    <hyperlink ref="C44" r:id="rId307" tooltip="https://www.amazon.es/dp/B0GQGFSN4B"/>
-    <hyperlink ref="G44" r:id="rId308" tooltip="https://www.amazon.es/X-cotec/b/ref=bl_dp_s_web_83579058031?ie=UTF8&amp;node=83579058031&amp;field-lbr_brands_browse-bin=X-cotec"/>
-    <hyperlink ref="J44" r:id="rId309" tooltip="https://www.amazon.es/dp/B0GQGFSN4B?psc=1"/>
-    <hyperlink ref="K44" r:id="rId310" tooltip="https://m.media-amazon.com/images/I/418leHoiDxL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId311" tooltip="https://www.amazon.es/dp/B0GR8DLV1X"/>
-    <hyperlink ref="M44" r:id="rId312" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N44" r:id="rId313"/>
-    <hyperlink ref="AW44" r:id="rId314" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3IGDW0WOTILEN"/>
-    <hyperlink ref="C45" r:id="rId315" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="G45" r:id="rId316" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId317" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K45" r:id="rId318" tooltip="https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId319" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="AW42" r:id="rId299" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
+    <hyperlink ref="C43" r:id="rId300" tooltip="https://www.amazon.es/dp/B0GQGFSN4B"/>
+    <hyperlink ref="G43" r:id="rId301" tooltip="https://www.amazon.es/X-cotec/b/ref=bl_dp_s_web_83579058031?ie=UTF8&amp;node=83579058031&amp;field-lbr_brands_browse-bin=X-cotec"/>
+    <hyperlink ref="J43" r:id="rId302" tooltip="https://www.amazon.es/dp/B0GQGFSN4B?psc=1"/>
+    <hyperlink ref="K43" r:id="rId303" tooltip="https://m.media-amazon.com/images/I/418leHoiDxL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId304" tooltip="https://www.amazon.es/dp/B0GR8DLV1X"/>
+    <hyperlink ref="M43" r:id="rId305" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N43" r:id="rId306"/>
+    <hyperlink ref="AW43" r:id="rId307" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3IGDW0WOTILEN"/>
+    <hyperlink ref="C44" r:id="rId308" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="G44" r:id="rId309" tooltip="https://www.amazon.es/stores/HAUSHOF/page/6370858C-87A5-4A8D-A835-FD7393C42C99?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId310" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K44" r:id="rId311" tooltip="https://m.media-amazon.com/images/I/41kdduO5uOL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId312" tooltip="https://www.amazon.es/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="M44" r:id="rId313" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N44" r:id="rId314"/>
+    <hyperlink ref="C45" r:id="rId315" tooltip="https://www.amazon.es/dp/B0DX2J6DW2"/>
+    <hyperlink ref="G45" r:id="rId316" tooltip="https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId317" tooltip="https://www.amazon.es/dp/B0DX2J6DW2?psc=1"/>
+    <hyperlink ref="K45" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId319" tooltip="https://www.amazon.es/dp/B0HJ99YM29"/>
     <hyperlink ref="M45" r:id="rId320" tooltip="https://www.amazon.es/b?node=3678039031"/>
     <hyperlink ref="N45" r:id="rId321"/>
-    <hyperlink ref="C46" r:id="rId322" tooltip="https://www.amazon.es/dp/B0DX2J6DW2"/>
-    <hyperlink ref="G46" r:id="rId323" tooltip="https://www.amazon.es/stores/Akitas/page/BEFA3F50-FB84-465F-816A-5D0B9DE2924B?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId324" tooltip="https://www.amazon.es/dp/B0DX2J6DW2?psc=1"/>
-    <hyperlink ref="K46" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/61nvuCA4-XL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId326" tooltip="https://www.amazon.es/dp/B0HJ99YM29"/>
-    <hyperlink ref="M46" r:id="rId327" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N46" r:id="rId328"/>
-    <hyperlink ref="AW46" r:id="rId329" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C47" r:id="rId330" tooltip="https://www.amazon.es/dp/B0DSC6DRWW"/>
-    <hyperlink ref="G47" r:id="rId331" tooltip="https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx"/>
-    <hyperlink ref="J47" r:id="rId332" tooltip="https://www.amazon.es/dp/B0DSC6DRWW?psc=1"/>
-    <hyperlink ref="K47" r:id="rId333" tooltip="https://m.media-amazon.com/images/I/41-sB8X-Z6L._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId334" tooltip="https://www.amazon.es/dp/B0H8J91VB1"/>
-    <hyperlink ref="M47" r:id="rId335" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N47" r:id="rId336"/>
-    <hyperlink ref="AW47" r:id="rId337" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K"/>
-    <hyperlink ref="C48" r:id="rId338" tooltip="https://www.amazon.es/dp/B0H9PTVK8F"/>
-    <hyperlink ref="G48" r:id="rId339" tooltip="https://www.amazon.es/stores/Respuestar%C3%A1pidaen24horas/page/E9B73071-F038-4416-BC9B-3CBCC33B0E9B?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId340" tooltip="https://www.amazon.es/dp/B0H9PTVK8F?psc=1"/>
-    <hyperlink ref="K48" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId342" tooltip="https://www.amazon.es/dp/B0HKMLWTQ6"/>
-    <hyperlink ref="M48" r:id="rId343" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N48" r:id="rId344"/>
-    <hyperlink ref="AW48" r:id="rId345" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
-    <hyperlink ref="C49" r:id="rId346" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
-    <hyperlink ref="G49" r:id="rId347" tooltip="https://www.amazon.es/stores/SharkINinja/page/A7BF4C0E-A1DC-446C-A093-0732B0FC27D7?lp_asin=B0FNRQFHWC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId348" tooltip="https://www.amazon.es/dp/B0FNRQFHWC?psc=1"/>
-    <hyperlink ref="K49" r:id="rId349" tooltip="https://images-na.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId350" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
-    <hyperlink ref="M49" r:id="rId351" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N49" r:id="rId352"/>
-    <hyperlink ref="AW49" r:id="rId353" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JJI37K279DYY"/>
-    <hyperlink ref="C50" r:id="rId354" tooltip="https://www.amazon.es/dp/B0HBCB6GRG"/>
-    <hyperlink ref="G50" r:id="rId355" tooltip="https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId356" tooltip="https://www.amazon.es/dp/B0HBCB6GRG?psc=1"/>
-    <hyperlink ref="K50" r:id="rId357" tooltip="https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId358" tooltip="https://www.amazon.es/dp/B0HKJPHGRM"/>
-    <hyperlink ref="M50" r:id="rId359" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N50" r:id="rId360"/>
-    <hyperlink ref="AW50" r:id="rId361" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08"/>
-    <hyperlink ref="C51" r:id="rId362" tooltip="https://www.amazon.es/dp/B0GNB36YF6"/>
-    <hyperlink ref="G51" r:id="rId363" tooltip="https://www.amazon.es/stores/Lom%C3%A1simportanteparatuhogar/page/0A2EDD59-3DB7-4014-B2F7-4216ECC1A033?lp_asin=B0GNB36YF6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId364" tooltip="https://www.amazon.es/dp/B0GNB36YF6?psc=1"/>
-    <hyperlink ref="K51" r:id="rId365" tooltip="https://m.media-amazon.com/images/I/41rp9ak74VL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId366" tooltip="https://www.amazon.es/dp/B0GNB36YF6"/>
-    <hyperlink ref="M51" r:id="rId367" tooltip="https://www.amazon.es/b?node=3678039031"/>
-    <hyperlink ref="N51" r:id="rId368"/>
-    <hyperlink ref="AW51" r:id="rId369" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25QV76UBVZPI4"/>
+    <hyperlink ref="AW45" r:id="rId322" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C46" r:id="rId323" tooltip="https://www.amazon.es/dp/B0DSC6DRWW"/>
+    <hyperlink ref="G46" r:id="rId324" tooltip="https://www.amazon.es/CLEANmaxx/b/ref=bl_dp_s_web_19531169031?ie=UTF8&amp;node=19531169031&amp;field-lbr_brands_browse-bin=CLEANmaxx"/>
+    <hyperlink ref="J46" r:id="rId325" tooltip="https://www.amazon.es/dp/B0DSC6DRWW?psc=1"/>
+    <hyperlink ref="K46" r:id="rId326" tooltip="https://m.media-amazon.com/images/I/41-sB8X-Z6L._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId327" tooltip="https://www.amazon.es/dp/B0H8J91VB1"/>
+    <hyperlink ref="M46" r:id="rId328" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N46" r:id="rId329"/>
+    <hyperlink ref="AW46" r:id="rId330" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSVGQQ89W56K"/>
+    <hyperlink ref="C47" r:id="rId331" tooltip="https://www.amazon.es/dp/B0H9PTVK8F"/>
+    <hyperlink ref="G47" r:id="rId332" tooltip="https://www.amazon.es/stores/Respuestar%C3%A1pidaen24horas/page/E9B73071-F038-4416-BC9B-3CBCC33B0E9B?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J47" r:id="rId333" tooltip="https://www.amazon.es/dp/B0H9PTVK8F?psc=1"/>
+    <hyperlink ref="K47" r:id="rId334" tooltip="https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId335" tooltip="https://www.amazon.es/dp/B0HKMLWTQ6"/>
+    <hyperlink ref="M47" r:id="rId336" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N47" r:id="rId337"/>
+    <hyperlink ref="AW47" r:id="rId338" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
+    <hyperlink ref="C48" r:id="rId339" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
+    <hyperlink ref="G48" r:id="rId340" tooltip="https://www.amazon.es/stores/SharkINinja/page/A7BF4C0E-A1DC-446C-A093-0732B0FC27D7?lp_asin=B0FNRQFHWC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId341" tooltip="https://www.amazon.es/dp/B0FNRQFHWC?psc=1"/>
+    <hyperlink ref="K48" r:id="rId342" tooltip="https://images-na.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId343" tooltip="https://www.amazon.es/dp/B0FNRQFHWC"/>
+    <hyperlink ref="M48" r:id="rId344" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N48" r:id="rId345"/>
+    <hyperlink ref="AW48" r:id="rId346" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JJI37K279DYY"/>
+    <hyperlink ref="C49" r:id="rId347" tooltip="https://www.amazon.es/dp/B0HBCB6GRG"/>
+    <hyperlink ref="G49" r:id="rId348" tooltip="https://www.amazon.es/stores/Circlio/page/7CE84697-9B97-4638-B272-BDC2206C39E4?lp_asin=B0HBCB6GRG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId349" tooltip="https://www.amazon.es/dp/B0HBCB6GRG?psc=1"/>
+    <hyperlink ref="K49" r:id="rId350" tooltip="https://m.media-amazon.com/images/I/41IC6EdxQZL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId351" tooltip="https://www.amazon.es/dp/B0HKJPHGRM"/>
+    <hyperlink ref="M49" r:id="rId352" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N49" r:id="rId353"/>
+    <hyperlink ref="AW49" r:id="rId354" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGQD5WZPQWZ08"/>
+    <hyperlink ref="C50" r:id="rId355" tooltip="https://www.amazon.es/dp/B0GNB36YF6"/>
+    <hyperlink ref="G50" r:id="rId356" tooltip="https://www.amazon.es/stores/Lom%C3%A1simportanteparatuhogar/page/0A2EDD59-3DB7-4014-B2F7-4216ECC1A033?lp_asin=B0GNB36YF6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J50" r:id="rId357" tooltip="https://www.amazon.es/dp/B0GNB36YF6?psc=1"/>
+    <hyperlink ref="K50" r:id="rId358" tooltip="https://m.media-amazon.com/images/I/41rp9ak74VL._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId359" tooltip="https://www.amazon.es/dp/B0GNB36YF6"/>
+    <hyperlink ref="M50" r:id="rId360" tooltip="https://www.amazon.es/b?node=3678039031"/>
+    <hyperlink ref="N50" r:id="rId361"/>
+    <hyperlink ref="AW50" r:id="rId362" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25QV76UBVZPI4"/>
   </hyperlinks>
-  <drawing r:id="rId370"/>
+  <drawing r:id="rId363"/>
 </worksheet>
 </file>
 
@@ -21052,7 +20759,7 @@
         <v>144.95367847411444</v>
       </c>
       <c r="G2" s="22">
-        <v>0.20721455457967378</v>
+        <v>0.20975423890264813</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21073,7 +20780,7 @@
         <v>82.52935458786936</v>
       </c>
       <c r="G3" s="22">
-        <v>0.3227101631116688</v>
+        <v>0.3266653965834762</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21094,7 +20801,7 @@
         <v>98.13422179914326</v>
       </c>
       <c r="G4" s="22">
-        <v>0.13180677540777916</v>
+        <v>0.13342223915666476</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21104,18 +20811,18 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <v>1177</v>
+        <v>984</v>
       </c>
       <c r="C5" s="15">
-        <v>115419</v>
+        <v>111561</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>98.06202209005947</v>
+        <v>113.375</v>
       </c>
       <c r="G5" s="22">
-        <v>0.07383939774153074</v>
+        <v>0.06248809297008954</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21136,7 +20843,7 @@
         <v>178.772397094431</v>
       </c>
       <c r="G6" s="22">
-        <v>0.025909661229611042</v>
+        <v>0.026227217882771322</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21157,7 +20864,7 @@
         <v>48.6175</v>
       </c>
       <c r="G7" s="22">
-        <v>0.07528230865746549</v>
+        <v>0.07620499142693847</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21178,7 +20885,7 @@
         <v>59.839590443686006</v>
       </c>
       <c r="G8" s="22">
-        <v>0.055144291091593474</v>
+        <v>0.055820156220232425</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21199,7 +20906,7 @@
         <v>89.9885496183206</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0164366373902133</v>
+        <v>0.016638089794881565</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21220,7 +20927,7 @@
         <v>65.99193548387096</v>
       </c>
       <c r="G10" s="22">
-        <v>0.015558343789209535</v>
+        <v>0.015749031561567282</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21241,7 +20948,7 @@
         <v>137.19387755102042</v>
       </c>
       <c r="G11" s="22">
-        <v>0.006148055207026349</v>
+        <v>0.0062234076331999745</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21262,7 +20969,7 @@
         <v>72.1829268292683</v>
       </c>
       <c r="G12" s="22">
-        <v>0.010288582183186951</v>
+        <v>0.01041468216168159</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21283,7 +20990,7 @@
         <v>169.98387096774192</v>
       </c>
       <c r="G13" s="22">
-        <v>0.0038895859473023838</v>
+        <v>0.003937257890391821</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21304,7 +21011,7 @@
         <v>89.99122807017544</v>
       </c>
       <c r="G14" s="22">
-        <v>0.007151819322459222</v>
+        <v>0.007239474185559154</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21325,7 +21032,7 @@
         <v>99.99</v>
       </c>
       <c r="G15" s="22">
-        <v>0.006273525721455458</v>
+        <v>0.006350415952244872</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21346,7 +21053,7 @@
         <v>69.90225563909775</v>
       </c>
       <c r="G16" s="22">
-        <v>0.00834378920953576</v>
+        <v>0.00844605321648568</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21367,7 +21074,7 @@
         <v>108.77464788732394</v>
       </c>
       <c r="G17" s="22">
-        <v>0.004454203262233375</v>
+        <v>0.004508795326093859</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21388,7 +21095,7 @@
         <v>148.5744680851064</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0029485570890840653</v>
+        <v>0.00298469549755509</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21409,7 +21116,7 @@
         <v>59.99065420560748</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0067126725219573405</v>
+        <v>0.006794945068902013</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21430,7 +21137,7 @@
         <v>79.98630136986301</v>
       </c>
       <c r="G20" s="22">
-        <v>0.004579673776662485</v>
+        <v>0.004635803645138757</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21451,7 +21158,7 @@
         <v>140.0</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0018820577164366374</v>
+        <v>0.0019051247856734616</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21472,7 +21179,7 @@
         <v>69.94444444444444</v>
       </c>
       <c r="G22" s="22">
-        <v>0.003387703889585947</v>
+        <v>0.003429224614212231</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21493,7 +21200,7 @@
         <v>72.72916666666667</v>
       </c>
       <c r="G23" s="22">
-        <v>0.00301129234629862</v>
+        <v>0.0030481996570775388</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21514,7 +21221,7 @@
         <v>80.0</v>
       </c>
       <c r="G24" s="22">
-        <v>0.0026348808030112925</v>
+        <v>0.0026671746999428463</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21535,7 +21242,7 @@
         <v>72.0</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0026348808030112925</v>
+        <v>0.0026671746999428463</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21556,7 +21263,7 @@
         <v>105.89473684210526</v>
       </c>
       <c r="G26" s="22">
-        <v>0.001191969887076537</v>
+        <v>0.0012065790309265256</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21577,7 +21284,7 @@
         <v>160.0</v>
       </c>
       <c r="G27" s="22">
-        <v>0.00018820577164366375</v>
+        <v>0.00019051247856734617</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21598,7 +21305,7 @@
         <v>75.0</v>
       </c>
       <c r="G28" s="22">
-        <v>0.0003764115432873275</v>
+        <v>0.00038102495713469235</v>
       </c>
     </row>
   </sheetData>
@@ -21662,18 +21369,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>12799</v>
+        <v>12606</v>
       </c>
       <c r="C2" s="15">
-        <v>1363897</v>
+        <v>1360039</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>106.56277834205797</v>
+        <v>107.8882278280184</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8029485570890841</v>
+        <v>0.8005334349399885</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21694,7 +21401,7 @@
         <v>48.6175</v>
       </c>
       <c r="G3" s="22">
-        <v>0.07528230865746549</v>
+        <v>0.07620499142693847</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21715,7 +21422,7 @@
         <v>59.839590443686006</v>
       </c>
       <c r="G4" s="22">
-        <v>0.055144291091593474</v>
+        <v>0.055820156220232425</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21736,7 +21443,7 @@
         <v>65.99193548387096</v>
       </c>
       <c r="G5" s="22">
-        <v>0.015558343789209535</v>
+        <v>0.015749031561567282</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21757,7 +21464,7 @@
         <v>72.1829268292683</v>
       </c>
       <c r="G6" s="22">
-        <v>0.010288582183186951</v>
+        <v>0.01041468216168159</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21778,7 +21485,7 @@
         <v>89.99122807017544</v>
       </c>
       <c r="G7" s="22">
-        <v>0.007151819322459222</v>
+        <v>0.007239474185559154</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21799,7 +21506,7 @@
         <v>99.99</v>
       </c>
       <c r="G8" s="22">
-        <v>0.006273525721455458</v>
+        <v>0.006350415952244872</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21820,7 +21527,7 @@
         <v>184.95833333333334</v>
       </c>
       <c r="G9" s="22">
-        <v>0.00301129234629862</v>
+        <v>0.0030481996570775388</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21841,7 +21548,7 @@
         <v>59.99065420560748</v>
       </c>
       <c r="G10" s="22">
-        <v>0.0067126725219573405</v>
+        <v>0.006794945068902013</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21862,7 +21569,7 @@
         <v>79.98630136986301</v>
       </c>
       <c r="G11" s="22">
-        <v>0.004579673776662485</v>
+        <v>0.004635803645138757</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21883,7 +21590,7 @@
         <v>140.0</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0018820577164366374</v>
+        <v>0.0019051247856734616</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21904,7 +21611,7 @@
         <v>69.94444444444444</v>
       </c>
       <c r="G13" s="22">
-        <v>0.003387703889585947</v>
+        <v>0.003429224614212231</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21925,7 +21632,7 @@
         <v>72.72916666666667</v>
       </c>
       <c r="G14" s="22">
-        <v>0.00301129234629862</v>
+        <v>0.0030481996570775388</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21946,7 +21653,7 @@
         <v>72.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0026348808030112925</v>
+        <v>0.0026671746999428463</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21967,7 +21674,7 @@
         <v>105.89473684210526</v>
       </c>
       <c r="G16" s="22">
-        <v>0.001191969887076537</v>
+        <v>0.0012065790309265256</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21988,7 +21695,7 @@
         <v>149.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0003764115432873275</v>
+        <v>0.00038102495713469235</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22009,7 +21716,7 @@
         <v>160.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.00018820577164366375</v>
+        <v>0.00019051247856734617</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22030,7 +21737,7 @@
         <v>75.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0003764115432873275</v>
+        <v>0.00038102495713469235</v>
       </c>
     </row>
   </sheetData>
